--- a/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chalmers-my.sharepoint.com/personal/larher_chalmers_se/Documents/Documents/GitHub/oa-tskr/Bibsam_tidskriftslistor/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_DBF5044DF6331EE0CE2416F094DF557850B45D8B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A407092-921E-4037-8E6D-5BC54071755C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014678EA-C9F1-4D3B-81A3-0B06BB7C71BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="5" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="214">
   <si>
     <t>Imprint</t>
   </si>
@@ -120,9 +120,6 @@
     <t>Archives of Disease in Childhood</t>
   </si>
   <si>
-    <t>http://.adc.bmj.com</t>
-  </si>
-  <si>
     <t>http://bjsm.bmj.com</t>
   </si>
   <si>
@@ -613,6 +610,63 @@
   </si>
   <si>
     <t>https://bmjdigitalhealth.bmj.com/</t>
+  </si>
+  <si>
+    <t>https://adc.bmj.com</t>
+  </si>
+  <si>
+    <t>2755-6166</t>
+  </si>
+  <si>
+    <t>BMJ Connections Digital Health &amp; AI</t>
+  </si>
+  <si>
+    <t>https://connectionsdigitalhealth.bmj.com/</t>
+  </si>
+  <si>
+    <t>2977-5876</t>
+  </si>
+  <si>
+    <t>BMJ Connections Immunology</t>
+  </si>
+  <si>
+    <t>https://connectionsimmunology.bmj.com/</t>
+  </si>
+  <si>
+    <t>2977-7798</t>
+  </si>
+  <si>
+    <t>BMJ Connections Mental Health</t>
+  </si>
+  <si>
+    <t>https://connectionsmentalhealth.bmj.com/</t>
+  </si>
+  <si>
+    <t>2978-1833</t>
+  </si>
+  <si>
+    <t>Gut Science</t>
+  </si>
+  <si>
+    <t>https://gutscience.bmj.com/</t>
+  </si>
+  <si>
+    <t>3049-8600</t>
+  </si>
+  <si>
+    <t>JME Practical Bioethics</t>
+  </si>
+  <si>
+    <t>https://jmepb.bmj.com/</t>
+  </si>
+  <si>
+    <t>2516-5410</t>
+  </si>
+  <si>
+    <t>World Journal of Pediatric Surgery</t>
+  </si>
+  <si>
+    <t>https://wjps.bmj.com/</t>
   </si>
 </sst>
 </file>
@@ -668,19 +722,19 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CC22B705-AC7C-40BC-8435-CA1F429C4808}" name="Table1" displayName="Table1" ref="A1:G62" totalsRowShown="0">
-  <autoFilter ref="A1:G62" xr:uid="{CC22B705-AC7C-40BC-8435-CA1F429C4808}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G62">
-    <sortCondition ref="D1:D62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}" name="Table2" displayName="Table2" ref="A1:G68" totalsRowShown="0">
+  <autoFilter ref="A1:G68" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G68">
+    <sortCondition ref="D1:D68"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{12B02975-ED55-4E2C-A0DC-05E25DA91B1A}" name="Imprint"/>
-    <tableColumn id="2" xr3:uid="{916506D8-61A3-4754-B028-B55EEC8CEB62}" name="ISSN Electronic"/>
-    <tableColumn id="3" xr3:uid="{DC5761CB-5DD6-471D-BC4C-E6349E27D7E0}" name="ISSN Print"/>
-    <tableColumn id="4" xr3:uid="{6B4BDCF7-EA44-4DE2-885B-9D88F00A9F00}" name="Journal Name"/>
-    <tableColumn id="5" xr3:uid="{9A04EE1C-E8E2-484E-B408-C122859BE177}" name="JournalURL"/>
-    <tableColumn id="6" xr3:uid="{FEFBD4DC-8E9D-40E7-A525-127249765BF6}" name="Publishing model"/>
-    <tableColumn id="7" xr3:uid="{AB61817C-3702-4113-AA53-F8FAC3372AAE}" name="CC License options"/>
+    <tableColumn id="1" xr3:uid="{E5C5B8A3-36BA-4BBD-9298-00857AB8D62A}" name="Imprint"/>
+    <tableColumn id="2" xr3:uid="{C06CCB14-E05F-4FFA-97FC-CF6D3A95D3F2}" name="ISSN Electronic"/>
+    <tableColumn id="3" xr3:uid="{254055E5-7A0A-41BE-8FDB-151499665899}" name="ISSN Print"/>
+    <tableColumn id="4" xr3:uid="{0AED8734-3B40-4036-BA17-8C7CB064678E}" name="Journal Name"/>
+    <tableColumn id="5" xr3:uid="{F9F1232A-B766-486B-BF14-AE5246005DF2}" name="JournalURL"/>
+    <tableColumn id="6" xr3:uid="{6F1193A3-CBC4-4E5B-B01A-FA299470EF3C}" name="Publishing model"/>
+    <tableColumn id="7" xr3:uid="{8304114F-D050-4C8F-BEC1-79D2538E6752}" name="CC License options"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -948,8 +1002,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DEAECD5-F60A-4D1F-8086-508739D77BB7}">
-  <dimension ref="A1:G62"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD2F074-D03B-498D-B3FD-BCFD8ABC303C}">
+  <dimension ref="A1:G68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -986,7 +1040,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
@@ -995,613 +1049,610 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="D5" t="s">
         <v>181</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>182</v>
       </c>
-      <c r="E5" t="s">
-        <v>183</v>
-      </c>
       <c r="F5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="D6" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="D7" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>202</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>203</v>
       </c>
       <c r="E8" t="s">
-        <v>102</v>
+        <v>204</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G8" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>184</v>
       </c>
       <c r="E9" t="s">
-        <v>71</v>
+        <v>185</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G9" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>112</v>
+        <v>192</v>
       </c>
       <c r="D10" t="s">
-        <v>72</v>
+        <v>193</v>
       </c>
       <c r="E10" t="s">
-        <v>73</v>
+        <v>194</v>
       </c>
       <c r="F10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G10" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="F11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>158</v>
+        <v>110</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>159</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>71</v>
       </c>
       <c r="E13" t="s">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="F13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="E14" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
       <c r="F14" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G14" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D15" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E15" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="D17" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="E17" t="s">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D18" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="F18" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
-        <v>77</v>
+        <v>141</v>
       </c>
       <c r="F19" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G19" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="E20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G20" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>154</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D22" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E22" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="F22" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E23" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="F23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G23" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D24" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E25" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="D27" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="D28" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E28" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="F28" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="D29" t="s">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="E29" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G29" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="D30" t="s">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="E30" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="F30" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="D31" t="s">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="E31" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" t="s">
-        <v>11</v>
+        <v>168</v>
       </c>
       <c r="D32" t="s">
-        <v>67</v>
+        <v>150</v>
       </c>
       <c r="E32" t="s">
-        <v>103</v>
+        <v>161</v>
       </c>
       <c r="F32" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G32" t="s">
         <v>108</v>
@@ -1609,139 +1660,142 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
-        <v>63</v>
+        <v>151</v>
       </c>
       <c r="E33" t="s">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>187</v>
+        <v>121</v>
       </c>
       <c r="D34" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="E34" t="s">
-        <v>189</v>
+        <v>132</v>
       </c>
       <c r="F34" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G34" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>127</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>191</v>
+        <v>66</v>
       </c>
       <c r="E35" t="s">
-        <v>192</v>
+        <v>102</v>
       </c>
       <c r="F35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>62</v>
       </c>
       <c r="E36" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D37" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="E37" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D38" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>191</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G38" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>137</v>
+        <v>13</v>
       </c>
       <c r="D39" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="E39" t="s">
-        <v>134</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G39" t="s">
         <v>108</v>
@@ -1749,19 +1803,19 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>15</v>
+        <v>170</v>
       </c>
       <c r="D40" t="s">
-        <v>37</v>
+        <v>152</v>
       </c>
       <c r="E40" t="s">
-        <v>38</v>
+        <v>163</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G40" t="s">
         <v>108</v>
@@ -1769,19 +1823,19 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E41" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G41" t="s">
         <v>108</v>
@@ -1789,119 +1843,119 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="D42" t="s">
-        <v>41</v>
+        <v>128</v>
       </c>
       <c r="E42" t="s">
-        <v>42</v>
+        <v>133</v>
       </c>
       <c r="F42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>147</v>
+        <v>15</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>36</v>
       </c>
       <c r="E43" t="s">
-        <v>145</v>
+        <v>37</v>
       </c>
       <c r="F43" t="s">
+        <v>68</v>
+      </c>
+      <c r="G43" t="s">
         <v>107</v>
-      </c>
-      <c r="G43" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="D44" t="s">
-        <v>43</v>
+        <v>206</v>
       </c>
       <c r="E44" t="s">
-        <v>44</v>
+        <v>207</v>
       </c>
       <c r="F44" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G44" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="E45" t="s">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G45" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E46" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G46" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>208</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>209</v>
       </c>
       <c r="E47" t="s">
-        <v>49</v>
+        <v>210</v>
       </c>
       <c r="F47" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G47" t="s">
         <v>108</v>
@@ -1909,19 +1963,19 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="D48" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="E48" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="F48" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G48" t="s">
         <v>108</v>
@@ -1929,19 +1983,19 @@
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="F49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G49" t="s">
         <v>108</v>
@@ -1949,219 +2003,219 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="F50" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G50" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E51" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F51" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D52" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F52" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G52" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="E53" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="F53" t="s">
+        <v>68</v>
+      </c>
+      <c r="G53" t="s">
         <v>107</v>
-      </c>
-      <c r="G53" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E54" t="s">
-        <v>50</v>
+        <v>103</v>
       </c>
       <c r="F54" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G54" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>91</v>
       </c>
       <c r="E55" t="s">
-        <v>165</v>
+        <v>92</v>
       </c>
       <c r="F55" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G55" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E56" t="s">
-        <v>97</v>
+        <v>46</v>
       </c>
       <c r="F56" t="s">
-        <v>107</v>
+        <v>68</v>
       </c>
       <c r="G56" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E57" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F57" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G57" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D58" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="F58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E59" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F59" t="s">
+        <v>68</v>
+      </c>
+      <c r="G59" t="s">
         <v>107</v>
-      </c>
-      <c r="G59" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>27</v>
+        <v>171</v>
       </c>
       <c r="D60" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="E60" t="s">
-        <v>58</v>
+        <v>164</v>
       </c>
       <c r="F60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G60" t="s">
         <v>108</v>
@@ -2169,42 +2223,162 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>125</v>
       </c>
       <c r="D61" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="E61" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
       <c r="F61" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="G61" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" t="s">
+        <v>52</v>
+      </c>
+      <c r="E62" t="s">
+        <v>53</v>
+      </c>
+      <c r="F62" t="s">
+        <v>68</v>
+      </c>
+      <c r="G62" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="D63" t="s">
+        <v>97</v>
+      </c>
+      <c r="E63" t="s">
+        <v>98</v>
+      </c>
+      <c r="F63" t="s">
+        <v>106</v>
+      </c>
+      <c r="G63" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="s">
         <v>61</v>
       </c>
-      <c r="B62" t="s">
-        <v>123</v>
-      </c>
-      <c r="D62" t="s">
+      <c r="E64" t="s">
+        <v>29</v>
+      </c>
+      <c r="F64" t="s">
+        <v>106</v>
+      </c>
+      <c r="G64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>60</v>
+      </c>
+      <c r="B65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s">
+        <v>56</v>
+      </c>
+      <c r="E65" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" t="s">
+        <v>68</v>
+      </c>
+      <c r="G65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>60</v>
+      </c>
+      <c r="B66" t="s">
+        <v>28</v>
+      </c>
+      <c r="D66" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" t="s">
+        <v>59</v>
+      </c>
+      <c r="F66" t="s">
+        <v>68</v>
+      </c>
+      <c r="G66" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B67" t="s">
+        <v>122</v>
+      </c>
+      <c r="D67" t="s">
+        <v>99</v>
+      </c>
+      <c r="E67" t="s">
         <v>100</v>
       </c>
-      <c r="E62" t="s">
-        <v>101</v>
-      </c>
-      <c r="F62" t="s">
-        <v>107</v>
-      </c>
-      <c r="G62" t="s">
-        <v>109</v>
+      <c r="F67" t="s">
+        <v>106</v>
+      </c>
+      <c r="G67" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>60</v>
+      </c>
+      <c r="B68" t="s">
+        <v>211</v>
+      </c>
+      <c r="D68" t="s">
+        <v>212</v>
+      </c>
+      <c r="E68" t="s">
+        <v>213</v>
+      </c>
+      <c r="F68" t="s">
+        <v>106</v>
+      </c>
+      <c r="G68" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014678EA-C9F1-4D3B-81A3-0B06BB7C71BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D88A2E3-3CB9-4307-AA24-6AE497D36F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -390,9 +390,6 @@
     <t>2399-9772</t>
   </si>
   <si>
-    <t>2631-4940</t>
-  </si>
-  <si>
     <t>2397-5776</t>
   </si>
   <si>
@@ -420,12 +417,6 @@
     <t>Journal of NeuroInterventional Surgery</t>
   </si>
   <si>
-    <t>BMJ Surgery, Interventions, &amp; Health Technologies</t>
-  </si>
-  <si>
-    <t>https://sit.bmj.com/</t>
-  </si>
-  <si>
     <t>https://fg.bmj.com/</t>
   </si>
   <si>
@@ -667,6 +658,15 @@
   </si>
   <si>
     <t>https://wjps.bmj.com/</t>
+  </si>
+  <si>
+    <t>2978-1809</t>
+  </si>
+  <si>
+    <t>BMJ Connections Surgery</t>
+  </si>
+  <si>
+    <t>https://connectionssurgery.bmj.com/</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1049,7 @@
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F2" t="s">
         <v>68</v>
@@ -1066,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E3" t="s">
         <v>104</v>
@@ -1086,7 +1086,7 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E4" t="s">
         <v>105</v>
@@ -1103,13 +1103,13 @@
         <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F5" t="s">
         <v>106</v>
@@ -1123,13 +1123,13 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="D6" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F6" t="s">
         <v>106</v>
@@ -1143,13 +1143,13 @@
         <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E7" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F7" t="s">
         <v>106</v>
@@ -1163,13 +1163,13 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D8" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E8" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F8" t="s">
         <v>106</v>
@@ -1183,13 +1183,13 @@
         <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
         <v>106</v>
@@ -1203,13 +1203,13 @@
         <v>60</v>
       </c>
       <c r="B10" t="s">
-        <v>192</v>
+        <v>211</v>
       </c>
       <c r="D10" t="s">
-        <v>193</v>
+        <v>212</v>
       </c>
       <c r="E10" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="F10" t="s">
         <v>106</v>
@@ -1223,16 +1223,16 @@
         <v>60</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>190</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G11" t="s">
         <v>108</v>
@@ -1243,16 +1243,16 @@
         <v>60</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="F12" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G12" t="s">
         <v>108</v>
@@ -1263,13 +1263,13 @@
         <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
         <v>106</v>
@@ -1283,16 +1283,16 @@
         <v>60</v>
       </c>
       <c r="B14" t="s">
-        <v>155</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G14" t="s">
         <v>108</v>
@@ -1303,13 +1303,13 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E15" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="F15" t="s">
         <v>68</v>
@@ -1323,16 +1323,16 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="F16" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G16" t="s">
         <v>108</v>
@@ -1343,13 +1343,13 @@
         <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>172</v>
+        <v>136</v>
       </c>
       <c r="D17" t="s">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="F17" t="s">
         <v>106</v>
@@ -1363,16 +1363,16 @@
         <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="E18" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="F18" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G18" t="s">
         <v>108</v>
@@ -1383,16 +1383,16 @@
         <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>142</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G19" t="s">
         <v>108</v>
@@ -1403,13 +1403,13 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F20" t="s">
         <v>106</v>
@@ -1423,13 +1423,13 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>165</v>
+        <v>112</v>
       </c>
       <c r="D21" t="s">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="E21" t="s">
-        <v>166</v>
+        <v>74</v>
       </c>
       <c r="F21" t="s">
         <v>106</v>
@@ -1443,13 +1443,13 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="F22" t="s">
         <v>106</v>
@@ -1463,13 +1463,13 @@
         <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D23" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E23" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F23" t="s">
         <v>106</v>
@@ -1483,13 +1483,13 @@
         <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
         <v>106</v>
@@ -1503,13 +1503,13 @@
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D25" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F25" t="s">
         <v>106</v>
@@ -1523,13 +1523,13 @@
         <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D26" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
         <v>106</v>
@@ -1543,13 +1543,13 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F27" t="s">
         <v>106</v>
@@ -1563,13 +1563,13 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F28" t="s">
         <v>106</v>
@@ -1583,13 +1583,13 @@
         <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
         <v>106</v>
@@ -1603,13 +1603,13 @@
         <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="D30" t="s">
-        <v>176</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
         <v>106</v>
@@ -1623,16 +1623,16 @@
         <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="E31" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G31" t="s">
         <v>108</v>
@@ -1643,13 +1643,13 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D32" t="s">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
-        <v>161</v>
+        <v>55</v>
       </c>
       <c r="F32" t="s">
         <v>68</v>
@@ -1663,13 +1663,13 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D33" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E33" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>68</v>
@@ -1683,16 +1683,16 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>121</v>
+        <v>166</v>
       </c>
       <c r="D34" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="E34" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="F34" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G34" t="s">
         <v>108</v>
@@ -1703,7 +1703,7 @@
         <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -1746,13 +1746,13 @@
         <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D37" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E37" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F37" t="s">
         <v>68</v>
@@ -1766,13 +1766,13 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D38" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E38" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F38" t="s">
         <v>68</v>
@@ -1806,13 +1806,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D40" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E40" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F40" t="s">
         <v>68</v>
@@ -1846,13 +1846,13 @@
         <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E42" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F42" t="s">
         <v>68</v>
@@ -1886,13 +1886,13 @@
         <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D44" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F44" t="s">
         <v>106</v>
@@ -1946,13 +1946,13 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D47" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E47" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F47" t="s">
         <v>106</v>
@@ -1966,13 +1966,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D48" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E48" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F48" t="s">
         <v>106</v>
@@ -2009,10 +2009,10 @@
         <v>19</v>
       </c>
       <c r="D50" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F50" t="s">
         <v>68</v>
@@ -2069,10 +2069,10 @@
         <v>25</v>
       </c>
       <c r="D53" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E53" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F53" t="s">
         <v>68</v>
@@ -2106,7 +2106,7 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
         <v>91</v>
@@ -2166,7 +2166,7 @@
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D58" t="s">
         <v>93</v>
@@ -2206,13 +2206,13 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D60" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E60" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F60" t="s">
         <v>68</v>
@@ -2226,7 +2226,7 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D61" t="s">
         <v>95</v>
@@ -2246,7 +2246,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D62" t="s">
         <v>52</v>
@@ -2266,7 +2266,7 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D63" t="s">
         <v>97</v>
@@ -2346,7 +2346,7 @@
         <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D67" t="s">
         <v>99</v>
@@ -2366,13 +2366,13 @@
         <v>60</v>
       </c>
       <c r="B68" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D68" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E68" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F68" t="s">
         <v>106</v>

--- a/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
+++ b/Bibsam_tidskriftslistor/scifree_data_bmj.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\larher\Documents\GitHub\oa-tskr\Bibsam_tidskriftslistor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D88A2E3-3CB9-4307-AA24-6AE497D36F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B9799DD-270F-4A80-89BB-11379170CB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="220">
   <si>
     <t>Imprint</t>
   </si>
@@ -667,6 +667,24 @@
   </si>
   <si>
     <t>https://connectionssurgery.bmj.com/</t>
+  </si>
+  <si>
+    <t>2977-5884</t>
+  </si>
+  <si>
+    <t>BMJ Immunology</t>
+  </si>
+  <si>
+    <t>https://bmjimmunology.bmj.com/</t>
+  </si>
+  <si>
+    <t>2755-6670</t>
+  </si>
+  <si>
+    <t>Lifestyle Medicine Advances</t>
+  </si>
+  <si>
+    <t>https://lifestylemedicine.bmj.com/</t>
   </si>
 </sst>
 </file>
@@ -722,10 +740,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}" name="Table2" displayName="Table2" ref="A1:G68" totalsRowShown="0">
-  <autoFilter ref="A1:G68" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G68">
-    <sortCondition ref="D1:D68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}" name="Table2" displayName="Table2" ref="A1:G70" totalsRowShown="0">
+  <autoFilter ref="A1:G70" xr:uid="{8422CCD4-1A46-4BE9-B19D-985F3D2DC7C6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G70">
+    <sortCondition ref="D1:D70"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E5C5B8A3-36BA-4BBD-9298-00857AB8D62A}" name="Imprint"/>
@@ -1003,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBD2F074-D03B-498D-B3FD-BCFD8ABC303C}">
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.7109375" customWidth="1"/>
@@ -1303,13 +1321,13 @@
         <v>60</v>
       </c>
       <c r="B15" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>215</v>
       </c>
       <c r="E15" t="s">
-        <v>153</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
         <v>68</v>
@@ -1323,13 +1341,13 @@
         <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F16" t="s">
         <v>68</v>
@@ -1343,16 +1361,16 @@
         <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="D17" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="E17" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="F17" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G17" t="s">
         <v>108</v>
@@ -1363,13 +1381,13 @@
         <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="D18" t="s">
-        <v>170</v>
+        <v>134</v>
       </c>
       <c r="E18" t="s">
-        <v>171</v>
+        <v>135</v>
       </c>
       <c r="F18" t="s">
         <v>106</v>
@@ -1383,16 +1401,16 @@
         <v>60</v>
       </c>
       <c r="B19" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="E19" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G19" t="s">
         <v>108</v>
@@ -1403,16 +1421,16 @@
         <v>60</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="D20" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
-        <v>138</v>
+        <v>157</v>
       </c>
       <c r="F20" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G20" t="s">
         <v>108</v>
@@ -1423,13 +1441,13 @@
         <v>60</v>
       </c>
       <c r="B21" t="s">
-        <v>112</v>
+        <v>139</v>
       </c>
       <c r="D21" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
       <c r="E21" t="s">
-        <v>74</v>
+        <v>138</v>
       </c>
       <c r="F21" t="s">
         <v>106</v>
@@ -1443,13 +1461,13 @@
         <v>60</v>
       </c>
       <c r="B22" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>73</v>
       </c>
       <c r="E22" t="s">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="F22" t="s">
         <v>106</v>
@@ -1463,13 +1481,13 @@
         <v>60</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>162</v>
       </c>
       <c r="D23" t="s">
-        <v>75</v>
+        <v>151</v>
       </c>
       <c r="E23" t="s">
-        <v>76</v>
+        <v>163</v>
       </c>
       <c r="F23" t="s">
         <v>106</v>
@@ -1483,13 +1501,13 @@
         <v>60</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E24" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F24" t="s">
         <v>106</v>
@@ -1503,13 +1521,13 @@
         <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F25" t="s">
         <v>106</v>
@@ -1523,13 +1541,13 @@
         <v>60</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F26" t="s">
         <v>106</v>
@@ -1543,13 +1561,13 @@
         <v>60</v>
       </c>
       <c r="B27" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F27" t="s">
         <v>106</v>
@@ -1563,13 +1581,13 @@
         <v>60</v>
       </c>
       <c r="B28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E28" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s">
         <v>106</v>
@@ -1583,13 +1601,13 @@
         <v>60</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s">
         <v>106</v>
@@ -1603,13 +1621,13 @@
         <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E30" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F30" t="s">
         <v>106</v>
@@ -1623,13 +1641,13 @@
         <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>174</v>
+        <v>90</v>
       </c>
       <c r="F31" t="s">
         <v>106</v>
@@ -1643,16 +1661,16 @@
         <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D32" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
       <c r="E32" t="s">
-        <v>55</v>
+        <v>174</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G32" t="s">
         <v>108</v>
@@ -1663,13 +1681,13 @@
         <v>60</v>
       </c>
       <c r="B33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D33" t="s">
-        <v>147</v>
+        <v>54</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>68</v>
@@ -1683,13 +1701,13 @@
         <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F34" t="s">
         <v>68</v>
@@ -1703,22 +1721,19 @@
         <v>60</v>
       </c>
       <c r="B35" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" t="s">
-        <v>11</v>
+        <v>166</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="F35" t="s">
         <v>68</v>
       </c>
       <c r="G35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -1726,19 +1741,22 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>126</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
       </c>
       <c r="D36" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="F36" t="s">
         <v>68</v>
       </c>
       <c r="G36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -1746,13 +1764,13 @@
         <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>183</v>
+        <v>12</v>
       </c>
       <c r="D37" t="s">
-        <v>184</v>
+        <v>62</v>
       </c>
       <c r="E37" t="s">
-        <v>185</v>
+        <v>31</v>
       </c>
       <c r="F37" t="s">
         <v>68</v>
@@ -1766,13 +1784,13 @@
         <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D38" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E38" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F38" t="s">
         <v>68</v>
@@ -1786,13 +1804,13 @@
         <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
       <c r="D39" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="E39" t="s">
-        <v>33</v>
+        <v>188</v>
       </c>
       <c r="F39" t="s">
         <v>68</v>
@@ -1806,13 +1824,13 @@
         <v>60</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
       <c r="D40" t="s">
-        <v>149</v>
+        <v>32</v>
       </c>
       <c r="E40" t="s">
-        <v>160</v>
+        <v>33</v>
       </c>
       <c r="F40" t="s">
         <v>68</v>
@@ -1826,13 +1844,13 @@
         <v>60</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="D41" t="s">
-        <v>34</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>35</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
         <v>68</v>
@@ -1846,19 +1864,19 @@
         <v>60</v>
       </c>
       <c r="B42" t="s">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>34</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="F42" t="s">
         <v>68</v>
       </c>
       <c r="G42" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
@@ -1866,13 +1884,13 @@
         <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>15</v>
+        <v>133</v>
       </c>
       <c r="D43" t="s">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="E43" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
       <c r="F43" t="s">
         <v>68</v>
@@ -1886,19 +1904,19 @@
         <v>60</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>15</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>36</v>
       </c>
       <c r="E44" t="s">
-        <v>204</v>
+        <v>37</v>
       </c>
       <c r="F44" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G44" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
@@ -1906,19 +1924,19 @@
         <v>60</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="D45" t="s">
-        <v>38</v>
+        <v>203</v>
       </c>
       <c r="E45" t="s">
-        <v>39</v>
+        <v>204</v>
       </c>
       <c r="F45" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G45" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
@@ -1926,19 +1944,19 @@
         <v>60</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F46" t="s">
         <v>68</v>
       </c>
       <c r="G46" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
@@ -1946,16 +1964,16 @@
         <v>60</v>
       </c>
       <c r="B47" t="s">
-        <v>205</v>
+        <v>17</v>
       </c>
       <c r="D47" t="s">
-        <v>206</v>
+        <v>40</v>
       </c>
       <c r="E47" t="s">
-        <v>207</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G47" t="s">
         <v>108</v>
@@ -1966,13 +1984,13 @@
         <v>60</v>
       </c>
       <c r="B48" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="D48" t="s">
-        <v>142</v>
+        <v>206</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="F48" t="s">
         <v>106</v>
@@ -1986,16 +2004,16 @@
         <v>60</v>
       </c>
       <c r="B49" t="s">
-        <v>18</v>
+        <v>143</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G49" t="s">
         <v>108</v>
@@ -2006,13 +2024,13 @@
         <v>60</v>
       </c>
       <c r="B50" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F50" t="s">
         <v>68</v>
@@ -2026,13 +2044,13 @@
         <v>60</v>
       </c>
       <c r="B51" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D51" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="E51" t="s">
-        <v>45</v>
+        <v>131</v>
       </c>
       <c r="F51" t="s">
         <v>68</v>
@@ -2046,19 +2064,19 @@
         <v>60</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D52" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E52" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F52" t="s">
         <v>68</v>
       </c>
       <c r="G52" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
@@ -2066,13 +2084,13 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D53" t="s">
-        <v>129</v>
+        <v>47</v>
       </c>
       <c r="E53" t="s">
-        <v>132</v>
+        <v>48</v>
       </c>
       <c r="F53" t="s">
         <v>68</v>
@@ -2086,13 +2104,13 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D54" t="s">
-        <v>67</v>
+        <v>129</v>
       </c>
       <c r="E54" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="F54" t="s">
         <v>68</v>
@@ -2106,19 +2124,19 @@
         <v>60</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>23</v>
       </c>
       <c r="D55" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="E55" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F55" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G55" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
@@ -2126,13 +2144,13 @@
         <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>218</v>
       </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>219</v>
       </c>
       <c r="F56" t="s">
         <v>68</v>
@@ -2146,16 +2164,16 @@
         <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>122</v>
       </c>
       <c r="D57" t="s">
-        <v>50</v>
+        <v>91</v>
       </c>
       <c r="E57" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="F57" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G57" t="s">
         <v>108</v>
@@ -2166,16 +2184,16 @@
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="E58" t="s">
-        <v>94</v>
+        <v>46</v>
       </c>
       <c r="F58" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G58" t="s">
         <v>108</v>
@@ -2186,19 +2204,19 @@
         <v>60</v>
       </c>
       <c r="B59" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E59" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F59" t="s">
         <v>68</v>
       </c>
       <c r="G59" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
@@ -2206,16 +2224,16 @@
         <v>60</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="D60" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="E60" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="F60" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G60" t="s">
         <v>108</v>
@@ -2226,19 +2244,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>124</v>
+        <v>24</v>
       </c>
       <c r="D61" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="E61" t="s">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="F61" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G61" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
@@ -2246,13 +2264,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>150</v>
       </c>
       <c r="E62" t="s">
-        <v>53</v>
+        <v>161</v>
       </c>
       <c r="F62" t="s">
         <v>68</v>
@@ -2266,13 +2284,13 @@
         <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D63" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E63" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F63" t="s">
         <v>106</v>
@@ -2286,16 +2304,16 @@
         <v>60</v>
       </c>
       <c r="B64" t="s">
-        <v>7</v>
+        <v>140</v>
       </c>
       <c r="D64" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E64" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F64" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G64" t="s">
         <v>108</v>
@@ -2306,19 +2324,19 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="E65" t="s">
-        <v>57</v>
+        <v>98</v>
       </c>
       <c r="F65" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G65" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
@@ -2326,16 +2344,16 @@
         <v>60</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D66" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E66" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F66" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="G66" t="s">
         <v>108</v>
@@ -2346,19 +2364,19 @@
         <v>60</v>
       </c>
       <c r="B67" t="s">
-        <v>121</v>
+        <v>27</v>
       </c>
       <c r="D67" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="E67" t="s">
-        <v>100</v>
+        <v>57</v>
       </c>
       <c r="F67" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="G67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
@@ -2366,18 +2384,58 @@
         <v>60</v>
       </c>
       <c r="B68" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" t="s">
+        <v>59</v>
+      </c>
+      <c r="F68" t="s">
+        <v>68</v>
+      </c>
+      <c r="G68" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>60</v>
+      </c>
+      <c r="B69" t="s">
+        <v>121</v>
+      </c>
+      <c r="D69" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" t="s">
+        <v>100</v>
+      </c>
+      <c r="F69" t="s">
+        <v>106</v>
+      </c>
+      <c r="G69" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>60</v>
+      </c>
+      <c r="B70" t="s">
         <v>208</v>
       </c>
-      <c r="D68" t="s">
+      <c r="D70" t="s">
         <v>209</v>
       </c>
-      <c r="E68" t="s">
+      <c r="E70" t="s">
         <v>210</v>
       </c>
-      <c r="F68" t="s">
-        <v>106</v>
-      </c>
-      <c r="G68" t="s">
+      <c r="F70" t="s">
+        <v>106</v>
+      </c>
+      <c r="G70" t="s">
         <v>108</v>
       </c>
     </row>
